--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI5"/>
+  <dimension ref="A1:BI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1331,203 +1331,6 @@
       </c>
       <c r="BI4" s="3" t="n">
         <v>46107.72916666666</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Cavalier</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dunbeholden</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="3" t="n">
-        <v>46107.75</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1331,6 +1331,203 @@
       </c>
       <c r="BI4" s="3" t="n">
         <v>46107.72916666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="3" t="n">
+        <v>46107.75</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI5"/>
+  <dimension ref="A1:BI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="BI2" s="3" t="n">
-        <v>46107.72916666666</v>
+        <v>46107.58333333334</v>
       </c>
     </row>
     <row r="3">
@@ -945,12 +945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,7 +994,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46107.72916666666</v>
+        <v>46107.66666666666</v>
       </c>
     </row>
     <row r="4">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,6 +1527,400 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
+        <v>46107.72916666666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="3" t="n">
+        <v>46107.72916666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="3" t="n">
         <v>46107.75</v>
       </c>
     </row>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="S6" t="n">
-        <v>4.28</v>
+        <v>3.06</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>2.48</v>
+        <v>4.24</v>
       </c>
       <c r="V6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.37</v>
       </c>
-      <c r="W6" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="R7" t="n">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="S7" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="T7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="X7" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="BD7" t="n">
         <v>3.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
         <v>1.16</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.53</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>2.51</v>
+        <v>4.24</v>
       </c>
       <c r="V5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.37</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.53</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.51</v>
+        <v>4.41</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.92</v>
+        <v>2.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>2.79</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R5" t="n">
+        <v>23</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.15</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="U5" t="n">
-        <v>4.24</v>
+        <v>24</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>4.3</v>
       </c>
       <c r="X5" t="n">
-        <v>3.58</v>
+        <v>2.05</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z5" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.34</v>
+        <v>5.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.15</v>
+        <v>1.96</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="AI5" t="n">
-        <v>10.5</v>
+        <v>3.08</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.13</v>
+        <v>3.34</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.71</v>
+        <v>1.54</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.79</v>
+        <v>6.1</v>
       </c>
       <c r="BE5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.37</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.07</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
         <v>5.29</v>
       </c>
       <c r="S7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="T7" t="n">
         <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>5.8</v>
+        <v>6.07</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X7" t="n">
         <v>2.88</v>
@@ -1816,34 +1816,34 @@
         <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
         <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AF7" t="n">
         <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.05</v>
@@ -1855,10 +1855,10 @@
         <v>1.74</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4.41</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>3.72</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.31</v>
+        <v>3.58</v>
       </c>
       <c r="AE4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2.7</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.67</v>
+        <v>1.92</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.79</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
+        <v>26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U5" t="n">
         <v>23</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>24</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
@@ -1416,10 +1416,10 @@
         <v>4.3</v>
       </c>
       <c r="X5" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
         <v>3.8</v>
@@ -1431,10 +1431,10 @@
         <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AE5" t="n">
         <v>1.36</v>
@@ -1443,28 +1443,28 @@
         <v>3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1509,16 +1509,16 @@
         <v>1.09</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BD5" t="n">
         <v>6.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="S6" t="n">
-        <v>4.28</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>2.97</v>
+        <v>2.13</v>
       </c>
       <c r="X6" t="n">
-        <v>2.44</v>
+        <v>3.76</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BC6" t="n">
-        <v>1.88</v>
+        <v>2.73</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>2.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>5.29</v>
+        <v>4.9</v>
       </c>
       <c r="S7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>6.07</v>
+        <v>5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
         <v>2.56</v>
       </c>
       <c r="X7" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
         <v>1.33</v>
@@ -1831,7 +1831,7 @@
         <v>3.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AF7" t="n">
         <v>1.72</v>
@@ -1849,16 +1849,16 @@
         <v>1.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>1.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.55</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.95</v>
+        <v>26</v>
       </c>
       <c r="S4" t="n">
-        <v>4.38</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.82</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>23</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC4" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>3.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
-        <v>26</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>4.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.82</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.18</v>
       </c>
-      <c r="W5" t="n">
+      <c r="BC5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.3</v>
       </c>
-      <c r="X5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="BE5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.42</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="S5" t="n">
-        <v>4.38</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>3.76</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.62</v>
       </c>
-      <c r="W6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AL6" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.73</v>
+        <v>1.92</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.07</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="R4" t="n">
-        <v>26</v>
+        <v>1.97</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>3.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.82</v>
+        <v>2.11</v>
       </c>
       <c r="U4" t="n">
-        <v>23</v>
+        <v>2.65</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>2.08</v>
+        <v>2.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.55</v>
+        <v>3.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.91</v>
+        <v>2.95</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.92</v>
+        <v>5.05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.04</v>
+        <v>1.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.9</v>
+        <v>1.28</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,58 +1392,58 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="S5" t="n">
         <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AH5" t="n">
         <v>1.09</v>
@@ -1455,67 +1455,67 @@
         <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AM5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.35</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.36</v>
       </c>
       <c r="BF5" t="n">
         <v>1.06</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.5</v>
+        <v>1.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>26</v>
       </c>
       <c r="S6" t="n">
-        <v>4.38</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC6" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,64 +1786,64 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>4.9</v>
+        <v>5.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="T7" t="n">
         <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y7" t="n">
         <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
         <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.65</v>
+        <v>6.4</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.05</v>
@@ -1852,13 +1852,13 @@
         <v>1.91</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="S4" t="n">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
@@ -1219,55 +1219,55 @@
         <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
         <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
         <v>3.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AL4" t="n">
         <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
         <v>2.88</v>
@@ -1404,22 +1404,22 @@
         <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="n">
-        <v>4.33</v>
+        <v>4.85</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
         <v>12</v>
@@ -1428,22 +1428,22 @@
         <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH5" t="n">
         <v>1.09</v>
@@ -1455,16 +1455,16 @@
         <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         <v>1.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF5" t="n">
         <v>1.06</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.06</v>
+        <v>1.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
-        <v>26</v>
+        <v>5.39</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.81</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>24</v>
+        <v>5.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="X6" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.21</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1</v>
-      </c>
       <c r="AN6" t="n">
-        <v>6.95</v>
+        <v>2.23</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46107.72916666666</v>
+        <v>46107.75</v>
       </c>
     </row>
     <row r="7">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="R7" t="n">
-        <v>5.39</v>
+        <v>26</v>
       </c>
       <c r="S7" t="n">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="X7" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.08</v>
+        <v>7.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>1.23</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.74</v>
+        <v>3.42</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.28</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AI7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AN7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM7" t="n">
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
         <v>1.06</v>
       </c>
-      <c r="AN7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BC7" t="n">
-        <v>2.13</v>
+        <v>1.48</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.62</v>
+        <v>2.73</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46107.75</v>
+        <v>46107.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,171 +1157,171 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>1.87</v>
+        <v>3.35</v>
       </c>
       <c r="S4" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W4" t="n">
         <v>2.14</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1.33</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AN4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC4" t="n">
         <v>2.75</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="BD4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,83 +1388,83 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.88</v>
       </c>
-      <c r="R5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.14</v>
-      </c>
       <c r="X5" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.27</v>
+        <v>3.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>

--- a/jogos_2026-03-26.xlsx
+++ b/jogos_2026-03-26.xlsx
@@ -1157,117 +1157,117 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.27</v>
+        <v>3.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,37 +1354,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.87</v>
+        <v>3.35</v>
       </c>
       <c r="S5" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.14</v>
       </c>
-      <c r="U5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.33</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
+      <c r="AN5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>2.75</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="BD5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1575,17 +1575,17 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Q7" t="n">
         <v>8.5</v>
       </c>
       <c r="R7" t="n">
-        <v>26</v>
+        <v>16.96</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB7" t="n">
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.16</v>
+        <v>2.79</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
